--- a/output/graficos_dimensiones/comunal_e_medianeta_a_2022_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_e_medianeta_a_2022_magallanes.xlsx
@@ -36,12 +36,12 @@
     <t xml:space="preserve">Magallanes</t>
   </si>
   <si>
+    <t xml:space="preserve">Timaukel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Río Verde</t>
   </si>
   <si>
-    <t xml:space="preserve">Timaukel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cabo de Hornos</t>
   </si>
   <si>
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:04</t>
+    <t xml:space="preserve">2026-09-10 00:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>12103</v>
+        <v>12303</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2022</v>
@@ -522,7 +522,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>12303</v>
+        <v>12103</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>

--- a/output/graficos_dimensiones/comunal_e_medianeta_a_2022_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_e_medianeta_a_2022_magallanes.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:06</t>
+    <t xml:space="preserve">2026-09-18 10:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
